--- a/Result/profitability/3373.xlsx
+++ b/Result/profitability/3373.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2375</v>
+        <v>-0.225</v>
       </c>
       <c r="N2" t="n">
-        <v>17.33625</v>
+        <v>17.01625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.08374999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>18.88625</v>
+        <v>19.01875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.66</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01000000000000002</v>
+        <v>0.05500000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>20.41125</v>
+        <v>21.52875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08750000000000002</v>
+        <v>0.14125</v>
       </c>
       <c r="N5" t="n">
-        <v>23.01375</v>
+        <v>22.93375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0.22875</v>
+        <v>0.24625</v>
       </c>
       <c r="N6" t="n">
-        <v>24.14125</v>
+        <v>23.93125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>0.31875</v>
+        <v>0.3275</v>
       </c>
       <c r="N7" t="n">
-        <v>25.71875</v>
+        <v>26.66625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4075</v>
+        <v>0.42875</v>
       </c>
       <c r="N8" t="n">
-        <v>27.895</v>
+        <v>28.535</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.61</v>
       </c>
       <c r="M11" t="n">
-        <v>0.54375</v>
+        <v>0.5437500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>31.425</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3373</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>121</v>
+      </c>
+      <c r="D75" t="n">
+        <v>98</v>
+      </c>
+      <c r="E75" t="n">
+        <v>23</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-6.60%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.6025</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6538461538461539</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.119999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.37345003646973</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8269230769230769</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.6400000000000006</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.03287108371854142</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
